--- a/Modelo_Planilha_Juntas.xlsx
+++ b/Modelo_Planilha_Juntas.xlsx
@@ -1,41 +1,212 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MORAIS\Documentos\GitHub\avanco-tubulacao\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE7356E-5D07-43CB-84D4-365B6B4A40B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="28680" yWindow="1680" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="MAPA_JUNTA" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="59">
+  <si>
+    <t>MAPA DE JUNTAS — MODELO</t>
+  </si>
+  <si>
+    <t>As linhas 1 a 7 são livres (título, logotipo etc.) — o sistema lê o cabeçalho a partir da linha 8.</t>
+  </si>
+  <si>
+    <t>unid</t>
+  </si>
+  <si>
+    <t>sth</t>
+  </si>
+  <si>
+    <t>isometrico</t>
+  </si>
+  <si>
+    <t>spool</t>
+  </si>
+  <si>
+    <t>junta</t>
+  </si>
+  <si>
+    <t>linha</t>
+  </si>
+  <si>
+    <t>diam</t>
+  </si>
+  <si>
+    <t>pol</t>
+  </si>
+  <si>
+    <t>tipo</t>
+  </si>
+  <si>
+    <t>asraiz</t>
+  </si>
+  <si>
+    <t>asench</t>
+  </si>
+  <si>
+    <t>dtsold</t>
+  </si>
+  <si>
+    <t>dtsoldr1</t>
+  </si>
+  <si>
+    <t>dtsoldr2</t>
+  </si>
+  <si>
+    <t>dt_lib_END</t>
+  </si>
+  <si>
+    <t>dtVS</t>
+  </si>
+  <si>
+    <t>dtUS</t>
+  </si>
+  <si>
+    <t>RX_US</t>
+  </si>
+  <si>
+    <t>mat</t>
+  </si>
+  <si>
+    <t>U4710</t>
+  </si>
+  <si>
+    <t>STH-4710-01</t>
+  </si>
+  <si>
+    <t>16"-HC-4710-05101-C5</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>J-0001</t>
+  </si>
+  <si>
+    <t>16"-HC-4710-05101-C5-AC</t>
+  </si>
+  <si>
+    <t>16"</t>
+  </si>
+  <si>
+    <t>Circular</t>
+  </si>
+  <si>
+    <t>J0000408</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>16"-HC-4710-05102-C5</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>J-0002</t>
+  </si>
+  <si>
+    <t>16"-HC-4710-05102-C5-AC</t>
+  </si>
+  <si>
+    <t>J0000539</t>
+  </si>
+  <si>
+    <t>STH-4710-02</t>
+  </si>
+  <si>
+    <t>4"-AI-4710-04146-C5</t>
+  </si>
+  <si>
+    <t>J-0003</t>
+  </si>
+  <si>
+    <t>4"-AI-4710-04146-C5-NI</t>
+  </si>
+  <si>
+    <t>4"</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>U4730</t>
+  </si>
+  <si>
+    <t>STH-4730-01</t>
+  </si>
+  <si>
+    <t>10"-HD-4730-05202-C5</t>
+  </si>
+  <si>
+    <t>J-0004</t>
+  </si>
+  <si>
+    <t>10"-HD-4730-05202-C5-AL</t>
+  </si>
+  <si>
+    <t>10"</t>
+  </si>
+  <si>
+    <t>T0000004</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>CIVIL</t>
+  </si>
+  <si>
+    <t>STH-CIVIL-01</t>
+  </si>
+  <si>
+    <t>2"-CV-CIVIL-00012-C5</t>
+  </si>
+  <si>
+    <t>J-0005</t>
+  </si>
+  <si>
+    <t>2"-CV-CIVIL-00012-C5-AC</t>
+  </si>
+  <si>
+    <t>2"</t>
+  </si>
+  <si>
+    <t>J0000261</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="166" formatCode="mm/dd/yy;@"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -43,13 +214,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,15 +249,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,349 +591,359 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="12.83203125" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" customWidth="1"/>
-    <col min="15" max="15" width="12.83203125" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1"/>
-    <col min="18" max="18" width="12.83203125" customWidth="1"/>
-    <col min="19" max="19" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="10.5" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.8984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.09765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.8984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.19921875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>MAPA DE JUNTAS — MODELO</v>
+    <row r="1" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>As linhas 1 a 7 são livres (título, logotipo etc.) — o sistema lê o cabeçalho a partir da linha 8.</v>
+    <row r="2" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>unid</v>
-      </c>
-      <c r="B8" t="str">
-        <v>sth</v>
-      </c>
-      <c r="C8" t="str">
-        <v>isometrico</v>
-      </c>
-      <c r="D8" t="str">
-        <v>spool</v>
-      </c>
-      <c r="E8" t="str">
-        <v>junta</v>
-      </c>
-      <c r="F8" t="str">
-        <v>linha</v>
-      </c>
-      <c r="G8" t="str">
-        <v>diam</v>
-      </c>
-      <c r="H8" t="str">
-        <v>pol</v>
-      </c>
-      <c r="I8" t="str">
-        <v>tipo</v>
-      </c>
-      <c r="J8" t="str">
-        <v>asraiz</v>
-      </c>
-      <c r="K8" t="str">
-        <v>asench</v>
-      </c>
-      <c r="L8" t="str">
-        <v>dtsold</v>
-      </c>
-      <c r="M8" t="str">
-        <v>dtsoldr1</v>
-      </c>
-      <c r="N8" t="str">
-        <v>dtsoldr2</v>
-      </c>
-      <c r="O8" t="str">
-        <v>dt_lib_END</v>
-      </c>
-      <c r="P8" t="str">
-        <v>dtVS</v>
-      </c>
-      <c r="Q8" t="str">
-        <v>dtUS</v>
-      </c>
-      <c r="R8" t="str">
-        <v>RX_US</v>
-      </c>
-      <c r="S8" t="str">
-        <v>mat</v>
+    <row r="8" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>U4710</v>
-      </c>
-      <c r="B9" t="str">
-        <v>STH-4710-01</v>
-      </c>
-      <c r="C9" t="str">
-        <v>16"-HC-4710-05101-C5</v>
-      </c>
-      <c r="D9" t="str">
-        <v>A</v>
-      </c>
-      <c r="E9" t="str">
-        <v>J-0001</v>
-      </c>
-      <c r="F9" t="str">
-        <v>16"-HC-4710-05101-C5-AC</v>
+    <row r="9" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
       </c>
       <c r="G9">
         <v>16</v>
       </c>
-      <c r="H9" t="str">
-        <v>16"</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Circular</v>
-      </c>
-      <c r="J9" t="str">
-        <v>J0000408</v>
-      </c>
-      <c r="L9" s="1">
-        <v>45365.99967592592</v>
-      </c>
-      <c r="O9" s="1">
-        <v>45370.99967592592</v>
-      </c>
-      <c r="P9" s="1">
-        <v>45366.99967592592</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>45369.99967592592</v>
-      </c>
-      <c r="R9" t="str">
-        <v>R</v>
-      </c>
-      <c r="S9" t="str">
-        <v>AC</v>
+      <c r="H9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" s="2">
+        <v>45365.999675925923</v>
+      </c>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2">
+        <v>45370.999675925923</v>
+      </c>
+      <c r="P9" s="2">
+        <v>45366.999675925923</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>45369.999675925923</v>
+      </c>
+      <c r="R9" t="s">
+        <v>30</v>
+      </c>
+      <c r="S9" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>U4710</v>
-      </c>
-      <c r="B10" t="str">
-        <v>STH-4710-01</v>
-      </c>
-      <c r="C10" t="str">
-        <v>16"-HC-4710-05102-C5</v>
-      </c>
-      <c r="D10" t="str">
-        <v>B</v>
-      </c>
-      <c r="E10" t="str">
-        <v>J-0002</v>
-      </c>
-      <c r="F10" t="str">
-        <v>16"-HC-4710-05102-C5-AC</v>
+    <row r="10" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" t="s">
+        <v>35</v>
       </c>
       <c r="G10">
         <v>16</v>
       </c>
-      <c r="H10" t="str">
-        <v>16"</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Circular</v>
-      </c>
-      <c r="J10" t="str">
-        <v>J0000539</v>
-      </c>
-      <c r="L10" s="1">
-        <v>45367.99967592592</v>
-      </c>
-      <c r="M10" s="1">
-        <v>45369.99967592592</v>
-      </c>
-      <c r="O10" s="1">
-        <v>45374.99967592592</v>
-      </c>
-      <c r="P10" s="1">
-        <v>45368.99967592592</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>45373.99967592592</v>
-      </c>
-      <c r="R10" t="str">
-        <v>R</v>
-      </c>
-      <c r="S10" t="str">
-        <v>AC</v>
+      <c r="H10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10" s="2">
+        <v>45367.999675925923</v>
+      </c>
+      <c r="M10" s="2">
+        <v>45369.999675925923</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2">
+        <v>45374.999675925923</v>
+      </c>
+      <c r="P10" s="2">
+        <v>45368.999675925923</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>45373.999675925923</v>
+      </c>
+      <c r="R10" t="s">
+        <v>30</v>
+      </c>
+      <c r="S10" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>U4710</v>
-      </c>
-      <c r="B11" t="str">
-        <v>STH-4710-02</v>
-      </c>
-      <c r="C11" t="str">
-        <v>4"-AI-4710-04146-C5</v>
-      </c>
-      <c r="D11" t="str">
-        <v>A</v>
-      </c>
-      <c r="E11" t="str">
-        <v>J-0003</v>
-      </c>
-      <c r="F11" t="str">
-        <v>4"-AI-4710-04146-C5-NI</v>
+    <row r="11" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" t="s">
+        <v>40</v>
       </c>
       <c r="G11">
         <v>4</v>
       </c>
-      <c r="H11" t="str">
-        <v>4"</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Circular</v>
-      </c>
-      <c r="R11" t="str">
-        <v>U</v>
-      </c>
-      <c r="S11" t="str">
-        <v>AI</v>
+      <c r="H11" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" t="s">
+        <v>42</v>
+      </c>
+      <c r="S11" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>U4730</v>
-      </c>
-      <c r="B12" t="str">
-        <v>STH-4730-01</v>
-      </c>
-      <c r="C12" t="str">
-        <v>10"-HD-4730-05202-C5</v>
-      </c>
-      <c r="D12" t="str">
-        <v>A</v>
-      </c>
-      <c r="E12" t="str">
-        <v>J-0004</v>
-      </c>
-      <c r="F12" t="str">
-        <v>10"-HD-4730-05202-C5-AL</v>
+    <row r="12" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" t="s">
+        <v>48</v>
       </c>
       <c r="G12">
         <v>10</v>
       </c>
-      <c r="H12" t="str">
-        <v>10"</v>
-      </c>
-      <c r="I12" t="str">
-        <v>Circular</v>
-      </c>
-      <c r="J12" t="str">
-        <v>T0000004</v>
-      </c>
-      <c r="L12" s="1">
-        <v>45391.99967592592</v>
-      </c>
-      <c r="M12" s="1">
-        <v>45393.99967592592</v>
-      </c>
-      <c r="N12" s="1">
-        <v>45395.99967592592</v>
-      </c>
-      <c r="O12" s="1">
-        <v>45399.99967592592</v>
-      </c>
-      <c r="P12" s="1">
-        <v>45392.99967592592</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>45398.99967592592</v>
-      </c>
-      <c r="R12" t="str">
-        <v>U</v>
-      </c>
-      <c r="S12" t="str">
-        <v>AL</v>
+      <c r="H12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" t="s">
+        <v>50</v>
+      </c>
+      <c r="L12" s="2">
+        <v>45391.999675925923</v>
+      </c>
+      <c r="M12" s="2">
+        <v>45393.999675925923</v>
+      </c>
+      <c r="N12" s="2">
+        <v>45395.999675925923</v>
+      </c>
+      <c r="O12" s="2">
+        <v>45399.999675925923</v>
+      </c>
+      <c r="P12" s="2">
+        <v>45392.999675925923</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>45398.999675925923</v>
+      </c>
+      <c r="R12" t="s">
+        <v>42</v>
+      </c>
+      <c r="S12" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>CIVIL</v>
-      </c>
-      <c r="B13" t="str">
-        <v>STH-CIVIL-01</v>
-      </c>
-      <c r="C13" t="str">
-        <v>2"-CV-CIVIL-00012-C5</v>
-      </c>
-      <c r="D13" t="str">
-        <v>A</v>
-      </c>
-      <c r="E13" t="str">
-        <v>J-0005</v>
-      </c>
-      <c r="F13" t="str">
-        <v>2"-CV-CIVIL-00012-C5-AC</v>
+    <row r="13" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" t="s">
+        <v>56</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
-      <c r="H13" t="str">
-        <v>2"</v>
-      </c>
-      <c r="I13" t="str">
-        <v>Circular</v>
-      </c>
-      <c r="J13" t="str">
-        <v>J0000261</v>
-      </c>
-      <c r="K13" t="str">
-        <v>J0000261</v>
-      </c>
-      <c r="L13" s="1">
-        <v>45308.99967592592</v>
-      </c>
-      <c r="O13" s="1">
-        <v>45315.99967592592</v>
-      </c>
-      <c r="P13" s="1">
-        <v>45309.99967592592</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>45314.99967592592</v>
-      </c>
-      <c r="R13" t="str">
-        <v>R</v>
-      </c>
-      <c r="S13" t="str">
-        <v>AC</v>
+      <c r="H13" t="s">
+        <v>57</v>
+      </c>
+      <c r="I13" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" t="s">
+        <v>58</v>
+      </c>
+      <c r="K13" t="s">
+        <v>58</v>
+      </c>
+      <c r="L13" s="2">
+        <v>45308.999675925923</v>
+      </c>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2">
+        <v>45315.999675925923</v>
+      </c>
+      <c r="P13" s="2">
+        <v>45309.999675925923</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>45314.999675925923</v>
+      </c>
+      <c r="R13" t="s">
+        <v>30</v>
+      </c>
+      <c r="S13" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S13"/>
+    <ignoredError sqref="A1:S13" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>